--- a/artfynd/A 23158-2025 artfynd.xlsx
+++ b/artfynd/A 23158-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17278156</v>
+        <v>114565484</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lunderåsberget, Mpd</t>
+          <t>Lappmon, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619694.4967427514</v>
+        <v>619744</v>
       </c>
       <c r="R2" t="n">
-        <v>6936045.732223185</v>
+        <v>6936141</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,82 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17278146</v>
+        <v>114565487</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lunderåsberget, Mpd</t>
+          <t>Lappmon, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619694.4967427514</v>
+        <v>619703</v>
       </c>
       <c r="R3" t="n">
-        <v>6936045.732223185</v>
+        <v>6936117</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-08-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,94 +853,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113283657</v>
+        <v>114565489</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Volmmyran, Rudtjärnen, Timrå, Mpd</t>
+          <t>Lappmon, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619575</v>
+        <v>619723</v>
       </c>
       <c r="R4" t="n">
-        <v>6936014</v>
+        <v>6936122</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,49 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Forsberg</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Forsberg</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114565484</v>
+        <v>114565490</v>
       </c>
       <c r="B5" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1083,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>619744</v>
+        <v>619742</v>
       </c>
       <c r="R5" t="n">
-        <v>6936141</v>
+        <v>6936088</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1145,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114565487</v>
+        <v>114565488</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1161,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>619703</v>
+        <v>619717</v>
       </c>
       <c r="R6" t="n">
-        <v>6936117</v>
+        <v>6936127</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1244,6 +1157,216 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114565491</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lappmon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>619731</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6936103</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113283657</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Volmmyran, Rudtjärnen, Timrå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>619575</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6936014</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Forsberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23158-2025 artfynd.xlsx
+++ b/artfynd/A 23158-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565484</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565487</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565489</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565490</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565488</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565491</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,8 +1402,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113283657</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>